--- a/Logger/Startzeitpunkt Messungen.xlsx
+++ b/Logger/Startzeitpunkt Messungen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Logger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CFB0F4-C218-45B4-B0A6-AAC68C64671B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09959E9-86C2-4764-9824-722FB898495E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D4C00000-9C7A-4673-AB29-681155B09424}"/>
   </bookViews>
@@ -132,7 +132,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,12 +142,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF66"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -342,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -362,19 +356,13 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -834,10 +822,10 @@
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="9">
         <v>45785</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="10">
         <v>45785</v>
       </c>
     </row>
@@ -856,10 +844,10 @@
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>23</v>
       </c>
     </row>
@@ -867,10 +855,10 @@
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="9">
         <v>45785</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="10">
         <v>45785</v>
       </c>
     </row>
@@ -878,10 +866,10 @@
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="9">
         <v>45785</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="10">
         <v>45785</v>
       </c>
     </row>
@@ -889,10 +877,10 @@
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="9">
         <v>45785</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="10">
         <v>45785</v>
       </c>
     </row>
@@ -900,10 +888,10 @@
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="10">
         <v>45785</v>
       </c>
     </row>
@@ -911,10 +899,10 @@
       <c r="A18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="11">
         <v>45800</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="12">
         <v>45800</v>
       </c>
     </row>
